--- a/results_three/results_three.xlsx
+++ b/results_three/results_three.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leticiadupleich/Desktop/Capstone/LeticiaCapstone/results_three/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A101BA3-4AD7-7E49-9834-6031F7878B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7346D161-9BD9-3145-812B-126770C0BABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{F1D71396-1DC3-294D-A1BC-F6200886B423}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16280" activeTab="3" xr2:uid="{F1D71396-1DC3-294D-A1BC-F6200886B423}"/>
   </bookViews>
   <sheets>
     <sheet name="time_overall" sheetId="1" r:id="rId1"/>
@@ -15053,18 +15053,18 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
       <sheetData sheetId="3">
         <row r="2">
           <cell r="A2" t="str">
-            <v>Elapsed Time</v>
+            <v>Execution Time</v>
           </cell>
           <cell r="B2" t="str">
             <v>CPU Time</v>
           </cell>
           <cell r="G2" t="str">
-            <v>Elapsed Time</v>
+            <v>Execution Time</v>
           </cell>
           <cell r="H2" t="str">
             <v>CPU Time</v>
@@ -16457,12 +16457,12 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
